--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J507"/>
+  <dimension ref="A1:J508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18685,9 +18685,45 @@
         <v>375.76</v>
       </c>
       <c r="I507" t="n">
-        <v>383.74</v>
+        <v>381.43</v>
       </c>
       <c r="J507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>362.56</v>
+      </c>
+      <c r="C508" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="D508" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="E508" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="F508" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="G508" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="H508" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="I508" t="n">
+        <v>380.62</v>
+      </c>
+      <c r="J508" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18704,7 +18740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24977,6 +25013,16 @@
       </c>
       <c r="B627" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -25145,28 +25191,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1884651376791234</v>
+        <v>-0.1930948845923491</v>
       </c>
       <c r="J2" t="n">
+        <v>507</v>
+      </c>
+      <c r="K2" t="n">
         <v>506</v>
       </c>
-      <c r="K2" t="n">
-        <v>505</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0238331014735611</v>
+        <v>0.02498973256375925</v>
       </c>
       <c r="M2" t="n">
-        <v>7.194315089959708</v>
+        <v>7.201053521271198</v>
       </c>
       <c r="N2" t="n">
-        <v>74.46560240135923</v>
+        <v>74.60284527450911</v>
       </c>
       <c r="O2" t="n">
-        <v>8.629345421372308</v>
+        <v>8.637293862924261</v>
       </c>
       <c r="P2" t="n">
-        <v>379.5475502600352</v>
+        <v>379.5992289218932</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25223,28 +25269,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2238462894577174</v>
+        <v>-0.2310699772294901</v>
       </c>
       <c r="J3" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02787803185034377</v>
+        <v>0.02954224831631502</v>
       </c>
       <c r="M3" t="n">
-        <v>7.732230634841893</v>
+        <v>7.753029809251409</v>
       </c>
       <c r="N3" t="n">
-        <v>88.70208897544799</v>
+        <v>89.21056516500937</v>
       </c>
       <c r="O3" t="n">
-        <v>9.418178644273423</v>
+        <v>9.445134470456701</v>
       </c>
       <c r="P3" t="n">
-        <v>382.2600816535793</v>
+        <v>382.3411316175309</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25301,28 +25347,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1649306237640395</v>
+        <v>-0.1696936843345758</v>
       </c>
       <c r="J4" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K4" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02085435329355423</v>
+        <v>0.02203256129015629</v>
       </c>
       <c r="M4" t="n">
-        <v>6.925148560448514</v>
+        <v>6.936884787329486</v>
       </c>
       <c r="N4" t="n">
-        <v>65.91205669263921</v>
+        <v>66.08669284644566</v>
       </c>
       <c r="O4" t="n">
-        <v>8.118624064004885</v>
+        <v>8.129372229541815</v>
       </c>
       <c r="P4" t="n">
-        <v>381.7159521916395</v>
+        <v>381.7688437997692</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25379,28 +25425,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2718193031552909</v>
+        <v>-0.2750259148732987</v>
       </c>
       <c r="J5" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K5" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05539982998280635</v>
+        <v>0.05673198938631108</v>
       </c>
       <c r="M5" t="n">
-        <v>6.745518321704496</v>
+        <v>6.748069026280058</v>
       </c>
       <c r="N5" t="n">
-        <v>65.01474548590112</v>
+        <v>65.02458395831982</v>
       </c>
       <c r="O5" t="n">
-        <v>8.063172172656436</v>
+        <v>8.06378223653887</v>
       </c>
       <c r="P5" t="n">
-        <v>376.3946997590994</v>
+        <v>376.4303077149298</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25457,28 +25503,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2750822008345895</v>
+        <v>-0.2766020815374511</v>
       </c>
       <c r="J6" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K6" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08612444324536628</v>
+        <v>0.08724175987367455</v>
       </c>
       <c r="M6" t="n">
-        <v>5.410513534660096</v>
+        <v>5.409065496828506</v>
       </c>
       <c r="N6" t="n">
-        <v>41.43785863167</v>
+        <v>41.38714659985352</v>
       </c>
       <c r="O6" t="n">
-        <v>6.437224450931472</v>
+        <v>6.433284277867218</v>
       </c>
       <c r="P6" t="n">
-        <v>374.7230629960018</v>
+        <v>374.7399405757322</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25535,28 +25581,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3442061309335711</v>
+        <v>-0.345085436515181</v>
       </c>
       <c r="J7" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K7" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1223611455298036</v>
+        <v>0.1232994227642914</v>
       </c>
       <c r="M7" t="n">
-        <v>5.422864821348877</v>
+        <v>5.417392427888239</v>
       </c>
       <c r="N7" t="n">
-        <v>43.85521058404198</v>
+        <v>43.77909348127589</v>
       </c>
       <c r="O7" t="n">
-        <v>6.622326674518706</v>
+        <v>6.616577172623009</v>
       </c>
       <c r="P7" t="n">
-        <v>382.8507423979358</v>
+        <v>382.8605066840625</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25613,28 +25659,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2216041531108726</v>
+        <v>-0.2221936318286452</v>
       </c>
       <c r="J8" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03769557691923253</v>
+        <v>0.03802647594760733</v>
       </c>
       <c r="M8" t="n">
-        <v>6.595621260356259</v>
+        <v>6.585712792719691</v>
       </c>
       <c r="N8" t="n">
-        <v>64.69780816134775</v>
+        <v>64.5748651425788</v>
       </c>
       <c r="O8" t="n">
-        <v>8.043494772879992</v>
+        <v>8.035848750603686</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2657328358396</v>
+        <v>382.2722787272637</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25691,28 +25737,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.202606189530828</v>
+        <v>-0.2033979600209461</v>
       </c>
       <c r="J9" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K9" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03141902802532126</v>
+        <v>0.03178473287136685</v>
       </c>
       <c r="M9" t="n">
-        <v>6.422240403610791</v>
+        <v>6.405942275562274</v>
       </c>
       <c r="N9" t="n">
-        <v>65.30708427595096</v>
+        <v>65.1583081286622</v>
       </c>
       <c r="O9" t="n">
-        <v>8.081279866206279</v>
+        <v>8.072069631058827</v>
       </c>
       <c r="P9" t="n">
-        <v>385.7065228880294</v>
+        <v>385.7153039166884</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25750,7 +25796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J507"/>
+  <dimension ref="A1:J508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52096,10 +52142,62 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>-45.76242259125005,170.67209784765228</t>
+          <t>-45.76244335446139,170.67209654281405</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-45.761762069980996,170.6661157695832</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-45.76207241357033,170.66686883086476</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-45.76218802711058,170.66771334726803</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-45.762316976281326,170.66856770826573</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-45.76239225823738,170.66946714615545</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-45.76244694728918,170.67036039808534</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-45.76248852721338,170.67121961376353</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-45.76245063506794,170.67209608527307</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J508"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18726,6 +18726,42 @@
       <c r="J508" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>357.02</v>
+      </c>
+      <c r="C509" t="n">
+        <v>354.83</v>
+      </c>
+      <c r="D509" t="n">
+        <v>359.92</v>
+      </c>
+      <c r="E509" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="F509" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="G509" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="H509" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="I509" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B628"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25023,6 +25059,16 @@
       </c>
       <c r="B628" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -25191,28 +25237,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1930948845923491</v>
+        <v>-0.199840482352175</v>
       </c>
       <c r="J2" t="n">
+        <v>508</v>
+      </c>
+      <c r="K2" t="n">
         <v>507</v>
       </c>
-      <c r="K2" t="n">
-        <v>506</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02498973256375925</v>
+        <v>0.0266116674186202</v>
       </c>
       <c r="M2" t="n">
-        <v>7.201053521271198</v>
+        <v>7.217180095078216</v>
       </c>
       <c r="N2" t="n">
-        <v>74.60284527450911</v>
+        <v>75.05513402114761</v>
       </c>
       <c r="O2" t="n">
-        <v>8.637293862924261</v>
+        <v>8.663436617252279</v>
       </c>
       <c r="P2" t="n">
-        <v>379.5992289218932</v>
+        <v>379.6748173483793</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25269,28 +25315,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2310699772294901</v>
+        <v>-0.2393926594406109</v>
       </c>
       <c r="J3" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02954224831631502</v>
+        <v>0.03145170251257123</v>
       </c>
       <c r="M3" t="n">
-        <v>7.753029809251409</v>
+        <v>7.77975853999226</v>
       </c>
       <c r="N3" t="n">
-        <v>89.21056516500937</v>
+        <v>89.93584669228021</v>
       </c>
       <c r="O3" t="n">
-        <v>9.445134470456701</v>
+        <v>9.483451201555276</v>
       </c>
       <c r="P3" t="n">
-        <v>382.3411316175309</v>
+        <v>382.4348719268922</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25347,28 +25393,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1696936843345758</v>
+        <v>-0.1763507404999496</v>
       </c>
       <c r="J4" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02203256129015629</v>
+        <v>0.02363667870699993</v>
       </c>
       <c r="M4" t="n">
-        <v>6.936884787329486</v>
+        <v>6.958352010833625</v>
       </c>
       <c r="N4" t="n">
-        <v>66.08669284644566</v>
+        <v>66.54743011777707</v>
       </c>
       <c r="O4" t="n">
-        <v>8.129372229541815</v>
+        <v>8.157660823899034</v>
       </c>
       <c r="P4" t="n">
-        <v>381.7688437997692</v>
+        <v>381.843056031121</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25425,28 +25471,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2750259148732987</v>
+        <v>-0.2799814926289418</v>
       </c>
       <c r="J5" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K5" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05673198938631108</v>
+        <v>0.05861010997870908</v>
       </c>
       <c r="M5" t="n">
-        <v>6.748069026280058</v>
+        <v>6.759058675058987</v>
       </c>
       <c r="N5" t="n">
-        <v>65.02458395831982</v>
+        <v>65.22398839748013</v>
       </c>
       <c r="O5" t="n">
-        <v>8.06378223653887</v>
+        <v>8.076136972431815</v>
       </c>
       <c r="P5" t="n">
-        <v>376.4303077149298</v>
+        <v>376.485552026191</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25503,28 +25549,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2766020815374511</v>
+        <v>-0.2797960419863806</v>
       </c>
       <c r="J6" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K6" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08724175987367455</v>
+        <v>0.08913560220755634</v>
       </c>
       <c r="M6" t="n">
-        <v>5.409065496828506</v>
+        <v>5.417619117280634</v>
       </c>
       <c r="N6" t="n">
-        <v>41.38714659985352</v>
+        <v>41.44168136863384</v>
       </c>
       <c r="O6" t="n">
-        <v>6.433284277867218</v>
+        <v>6.437521368402114</v>
       </c>
       <c r="P6" t="n">
-        <v>374.7399405757322</v>
+        <v>374.7755465441777</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25581,28 +25627,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.345085436515181</v>
+        <v>-0.3477141918844777</v>
       </c>
       <c r="J7" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K7" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1232994227642914</v>
+        <v>0.1251433193211817</v>
       </c>
       <c r="M7" t="n">
-        <v>5.417392427888239</v>
+        <v>5.422196301372704</v>
       </c>
       <c r="N7" t="n">
-        <v>43.77909348127589</v>
+        <v>43.78504347884426</v>
       </c>
       <c r="O7" t="n">
-        <v>6.616577172623009</v>
+        <v>6.617026785410821</v>
       </c>
       <c r="P7" t="n">
-        <v>382.8605066840625</v>
+        <v>382.8898117998355</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25659,28 +25705,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2221936318286452</v>
+        <v>-0.2240952825245346</v>
       </c>
       <c r="J8" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K8" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03802647594760733</v>
+        <v>0.03877138419923487</v>
       </c>
       <c r="M8" t="n">
-        <v>6.585712792719691</v>
+        <v>6.582663801477177</v>
       </c>
       <c r="N8" t="n">
-        <v>64.5748651425788</v>
+        <v>64.49596169306611</v>
       </c>
       <c r="O8" t="n">
-        <v>8.035848750603686</v>
+        <v>8.030937784161083</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2722787272637</v>
+        <v>382.2934781490333</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25737,28 +25783,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2033979600209461</v>
+        <v>-0.2050110410963633</v>
       </c>
       <c r="J9" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K9" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03178473287136685</v>
+        <v>0.03237917350910036</v>
       </c>
       <c r="M9" t="n">
-        <v>6.405942275562274</v>
+        <v>6.402565419253349</v>
       </c>
       <c r="N9" t="n">
-        <v>65.1583081286622</v>
+        <v>65.06473418918119</v>
       </c>
       <c r="O9" t="n">
-        <v>8.072069631058827</v>
+        <v>8.066271393226314</v>
       </c>
       <c r="P9" t="n">
-        <v>385.7153039166884</v>
+        <v>385.733286391672</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25796,7 +25842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J508"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52203,6 +52249,58 @@
         </is>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-45.76180619064306,170.66608263789925</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-45.76209648292571,170.66685411180234</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-45.76223160717698,170.6676974079284</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-45.76235789787273,170.66855728744622</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-45.76243114608462,170.66945589530172</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-45.762487646242384,170.67034966391742</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-45.762519432544735,170.67121548774625</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-45.76249090311381,170.67209355467327</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18760,6 +18760,42 @@
         <v>376.14</v>
       </c>
       <c r="J509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="C510" t="n">
+        <v>358.26</v>
+      </c>
+      <c r="D510" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="E510" t="n">
+        <v>356.66</v>
+      </c>
+      <c r="F510" t="n">
+        <v>359.4</v>
+      </c>
+      <c r="G510" t="n">
+        <v>366.36</v>
+      </c>
+      <c r="H510" t="n">
+        <v>371.32</v>
+      </c>
+      <c r="I510" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="J510" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18776,7 +18812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25069,6 +25105,16 @@
       </c>
       <c r="B629" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -25237,28 +25283,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.199840482352175</v>
+        <v>-0.2072600551057298</v>
       </c>
       <c r="J2" t="n">
+        <v>509</v>
+      </c>
+      <c r="K2" t="n">
         <v>508</v>
       </c>
-      <c r="K2" t="n">
-        <v>507</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0266116674186202</v>
+        <v>0.02841100544578778</v>
       </c>
       <c r="M2" t="n">
-        <v>7.217180095078216</v>
+        <v>7.236750702322619</v>
       </c>
       <c r="N2" t="n">
-        <v>75.05513402114761</v>
+        <v>75.62712566548673</v>
       </c>
       <c r="O2" t="n">
-        <v>8.663436617252279</v>
+        <v>8.69638578177663</v>
       </c>
       <c r="P2" t="n">
-        <v>379.6748173483793</v>
+        <v>379.7582858659469</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25315,28 +25361,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2393926594406109</v>
+        <v>-0.2463444679313249</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03145170251257123</v>
+        <v>0.03314745876181646</v>
       </c>
       <c r="M3" t="n">
-        <v>7.77975853999226</v>
+        <v>7.799288274970737</v>
       </c>
       <c r="N3" t="n">
-        <v>89.93584669228021</v>
+        <v>90.38274374007059</v>
       </c>
       <c r="O3" t="n">
-        <v>9.483451201555276</v>
+        <v>9.50698394550399</v>
       </c>
       <c r="P3" t="n">
-        <v>382.4348719268922</v>
+        <v>382.5134783353777</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25393,28 +25439,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1763507404999496</v>
+        <v>-0.1825134511953623</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02363667870699993</v>
+        <v>0.0251859601576454</v>
       </c>
       <c r="M4" t="n">
-        <v>6.958352010833625</v>
+        <v>6.97698918106117</v>
       </c>
       <c r="N4" t="n">
-        <v>66.54743011777707</v>
+        <v>66.9192235366706</v>
       </c>
       <c r="O4" t="n">
-        <v>8.157660823899034</v>
+        <v>8.180417075960772</v>
       </c>
       <c r="P4" t="n">
-        <v>381.843056031121</v>
+        <v>381.9120301156812</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25471,28 +25517,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2799814926289418</v>
+        <v>-0.2847525908786926</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05861010997870908</v>
+        <v>0.06046290595096038</v>
       </c>
       <c r="M5" t="n">
-        <v>6.759058675058987</v>
+        <v>6.76906722749494</v>
       </c>
       <c r="N5" t="n">
-        <v>65.22398839748013</v>
+        <v>65.3970500505233</v>
       </c>
       <c r="O5" t="n">
-        <v>8.076136972431815</v>
+        <v>8.086844257837745</v>
       </c>
       <c r="P5" t="n">
-        <v>376.485552026191</v>
+        <v>376.5389509524733</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25549,28 +25595,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2797960419863806</v>
+        <v>-0.2828607488741985</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08913560220755634</v>
+        <v>0.09099608135620285</v>
       </c>
       <c r="M6" t="n">
-        <v>5.417619117280634</v>
+        <v>5.42541047765085</v>
       </c>
       <c r="N6" t="n">
-        <v>41.44168136863384</v>
+        <v>41.48454333780987</v>
       </c>
       <c r="O6" t="n">
-        <v>6.437521368402114</v>
+        <v>6.440849581989156</v>
       </c>
       <c r="P6" t="n">
-        <v>374.7755465441777</v>
+        <v>374.8098472541217</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25627,28 +25673,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3477141918844777</v>
+        <v>-0.3505290932668703</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1251433193211817</v>
+        <v>0.1270878671028742</v>
       </c>
       <c r="M7" t="n">
-        <v>5.422196301372704</v>
+        <v>5.428053087538306</v>
       </c>
       <c r="N7" t="n">
-        <v>43.78504347884426</v>
+        <v>43.80386710570478</v>
       </c>
       <c r="O7" t="n">
-        <v>6.617026785410821</v>
+        <v>6.618448995475056</v>
       </c>
       <c r="P7" t="n">
-        <v>382.8898117998355</v>
+        <v>382.9213166449553</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25705,28 +25751,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2240952825245346</v>
+        <v>-0.2260319545544921</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03877138419923487</v>
+        <v>0.03953711506882873</v>
       </c>
       <c r="M8" t="n">
-        <v>6.582663801477177</v>
+        <v>6.579725499091253</v>
       </c>
       <c r="N8" t="n">
-        <v>64.49596169306611</v>
+        <v>64.41887949342278</v>
       </c>
       <c r="O8" t="n">
-        <v>8.030937784161083</v>
+        <v>8.026137271030366</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2934781490333</v>
+        <v>382.3151537049634</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25783,28 +25829,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2050110410963633</v>
+        <v>-0.2069510549045306</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03237917350910036</v>
+        <v>0.03307511605926294</v>
       </c>
       <c r="M9" t="n">
-        <v>6.402565419253349</v>
+        <v>6.400982130122848</v>
       </c>
       <c r="N9" t="n">
-        <v>65.06473418918119</v>
+        <v>64.98670597808453</v>
       </c>
       <c r="O9" t="n">
-        <v>8.066271393226314</v>
+        <v>8.061433245898929</v>
       </c>
       <c r="P9" t="n">
-        <v>385.733286391672</v>
+        <v>385.7549993493404</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25842,7 +25888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52301,6 +52347,58 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-45.761820605514046,170.66607181327615</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-45.7620681125169,170.66687146107384</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-45.762220973641064,170.66770129712964</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-45.76235417772813,170.66855823479415</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-45.76242858883396,170.6694566351543</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-45.76249242394548,170.67034840381837</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-45.76252059709343,170.67121533227302</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-45.762498812908476,170.6720930575906</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J510"/>
+  <dimension ref="A1:J512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18798,6 +18798,78 @@
       <c r="J510" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="C511" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="D511" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="E511" t="n">
+        <v>353.39</v>
+      </c>
+      <c r="F511" t="n">
+        <v>357.15</v>
+      </c>
+      <c r="G511" t="n">
+        <v>365</v>
+      </c>
+      <c r="H511" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="I511" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>346.14</v>
+      </c>
+      <c r="C512" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="D512" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="E512" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="F512" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="G512" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="H512" t="n">
+        <v>364.87</v>
+      </c>
+      <c r="I512" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B630"/>
+  <dimension ref="A1:B632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25115,6 +25187,26 @@
       </c>
       <c r="B630" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>
@@ -25283,28 +25375,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2072600551057298</v>
+        <v>-0.2283224710899068</v>
       </c>
       <c r="J2" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02841100544578778</v>
+        <v>0.03330236385666574</v>
       </c>
       <c r="M2" t="n">
-        <v>7.236750702322619</v>
+        <v>7.303305573768522</v>
       </c>
       <c r="N2" t="n">
-        <v>75.62712566548673</v>
+        <v>78.21627423934709</v>
       </c>
       <c r="O2" t="n">
-        <v>8.69638578177663</v>
+        <v>8.843996508329653</v>
       </c>
       <c r="P2" t="n">
-        <v>379.7582858659469</v>
+        <v>379.9962844799302</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25361,28 +25453,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2463444679313249</v>
+        <v>-0.2625665788423932</v>
       </c>
       <c r="J3" t="n">
+        <v>511</v>
+      </c>
+      <c r="K3" t="n">
         <v>509</v>
       </c>
-      <c r="K3" t="n">
-        <v>507</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03314745876181646</v>
+        <v>0.03710339183373734</v>
       </c>
       <c r="M3" t="n">
-        <v>7.799288274970737</v>
+        <v>7.849967445506723</v>
       </c>
       <c r="N3" t="n">
-        <v>90.38274374007059</v>
+        <v>91.72307432995753</v>
       </c>
       <c r="O3" t="n">
-        <v>9.50698394550399</v>
+        <v>9.577216418665579</v>
       </c>
       <c r="P3" t="n">
-        <v>382.5134783353777</v>
+        <v>382.6977173959022</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25439,28 +25531,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1825134511953623</v>
+        <v>-0.1984051258958729</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0251859601576454</v>
+        <v>0.02914813801063287</v>
       </c>
       <c r="M4" t="n">
-        <v>6.97698918106117</v>
+        <v>7.031927285074575</v>
       </c>
       <c r="N4" t="n">
-        <v>66.9192235366706</v>
+        <v>68.32345039277432</v>
       </c>
       <c r="O4" t="n">
-        <v>8.180417075960772</v>
+        <v>8.265800045535478</v>
       </c>
       <c r="P4" t="n">
-        <v>381.9120301156812</v>
+        <v>382.0906888938449</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25517,28 +25609,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2847525908786926</v>
+        <v>-0.2971523195651559</v>
       </c>
       <c r="J5" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K5" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06046290595096038</v>
+        <v>0.06503142350311431</v>
       </c>
       <c r="M5" t="n">
-        <v>6.76906722749494</v>
+        <v>6.803148341822792</v>
       </c>
       <c r="N5" t="n">
-        <v>65.3970500505233</v>
+        <v>66.15365850872945</v>
       </c>
       <c r="O5" t="n">
-        <v>8.086844257837745</v>
+        <v>8.133489934138325</v>
       </c>
       <c r="P5" t="n">
-        <v>376.5389509524733</v>
+        <v>376.6783510981872</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25595,28 +25687,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2828607488741985</v>
+        <v>-0.2910765563594597</v>
       </c>
       <c r="J6" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09099608135620285</v>
+        <v>0.09560040585267293</v>
       </c>
       <c r="M6" t="n">
-        <v>5.42541047765085</v>
+        <v>5.453493360829104</v>
       </c>
       <c r="N6" t="n">
-        <v>41.48454333780987</v>
+        <v>41.76735203252412</v>
       </c>
       <c r="O6" t="n">
-        <v>6.440849581989156</v>
+        <v>6.462766592762276</v>
       </c>
       <c r="P6" t="n">
-        <v>374.8098472541217</v>
+        <v>374.9022116045574</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25673,28 +25765,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3505290932668703</v>
+        <v>-0.3579976887173762</v>
       </c>
       <c r="J7" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K7" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1270878671028742</v>
+        <v>0.1317718394701806</v>
       </c>
       <c r="M7" t="n">
-        <v>5.428053087538306</v>
+        <v>5.450764108970623</v>
       </c>
       <c r="N7" t="n">
-        <v>43.80386710570478</v>
+        <v>44.00414309791073</v>
       </c>
       <c r="O7" t="n">
-        <v>6.618448995475056</v>
+        <v>6.633561871115</v>
       </c>
       <c r="P7" t="n">
-        <v>382.9213166449553</v>
+        <v>383.005282867989</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25751,28 +25843,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2260319545544921</v>
+        <v>-0.2336127548030375</v>
       </c>
       <c r="J8" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K8" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03953711506882873</v>
+        <v>0.04219564880169824</v>
       </c>
       <c r="M8" t="n">
-        <v>6.579725499091253</v>
+        <v>6.592732884239314</v>
       </c>
       <c r="N8" t="n">
-        <v>64.41887949342278</v>
+        <v>64.55414025921758</v>
       </c>
       <c r="O8" t="n">
-        <v>8.026137271030366</v>
+        <v>8.034559120400917</v>
       </c>
       <c r="P8" t="n">
-        <v>382.3151537049634</v>
+        <v>382.4003829478089</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25829,28 +25921,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2069510549045306</v>
+        <v>-0.2136154419333078</v>
       </c>
       <c r="J9" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K9" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03307511605926294</v>
+        <v>0.03527611213423243</v>
       </c>
       <c r="M9" t="n">
-        <v>6.400982130122848</v>
+        <v>6.413452178679852</v>
       </c>
       <c r="N9" t="n">
-        <v>64.98670597808453</v>
+        <v>65.02935841884057</v>
       </c>
       <c r="O9" t="n">
-        <v>8.061433245898929</v>
+        <v>8.06407827459782</v>
       </c>
       <c r="P9" t="n">
-        <v>385.7549993493404</v>
+        <v>385.8299246586285</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25888,7 +25980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J510"/>
+  <dimension ref="A1:J512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52399,6 +52491,110 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-45.76187945958839,170.66602761765657</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-45.7620839933292,170.6668617495305</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-45.76225269992805,170.66768969327862</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-45.76238314171083,170.66855085901042</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-45.76244842957177,170.66945089491693</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-45.76250445667913,170.67034523023452</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-45.76255042745634,170.67121134976423</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-45.76252191310422,170.67209160588217</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-45.76189283913167,170.66601757046595</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-45.76210425790601,170.66684935718834</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-45.76227283391703,170.66768232928905</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-45.76239341639565,170.66854824252252</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-45.762458394031036,170.6694480120405</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-45.762524363774915,170.67033997981682</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-45.762578376624866,170.67120761840025</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-45.76254213701089,170.67209033492995</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J512"/>
+  <dimension ref="A1:J513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18870,6 +18870,42 @@
       <c r="J512" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>347.12</v>
+      </c>
+      <c r="C513" t="n">
+        <v>350.21</v>
+      </c>
+      <c r="D513" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="E513" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="F513" t="n">
+        <v>353.19</v>
+      </c>
+      <c r="G513" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="H513" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="I513" t="n">
+        <v>364.91</v>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18884,7 +18920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B632"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25207,6 +25243,16 @@
       </c>
       <c r="B632" t="n">
         <v>-0.88</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -25375,28 +25421,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2283224710899068</v>
+        <v>-0.2386819539853118</v>
       </c>
       <c r="J2" t="n">
+        <v>512</v>
+      </c>
+      <c r="K2" t="n">
         <v>511</v>
       </c>
-      <c r="K2" t="n">
-        <v>510</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03330236385666574</v>
+        <v>0.03580279417014387</v>
       </c>
       <c r="M2" t="n">
-        <v>7.303305573768522</v>
+        <v>7.335862062742941</v>
       </c>
       <c r="N2" t="n">
-        <v>78.21627423934709</v>
+        <v>79.4596707374865</v>
       </c>
       <c r="O2" t="n">
-        <v>8.843996508329653</v>
+        <v>8.914015410435777</v>
       </c>
       <c r="P2" t="n">
-        <v>379.9962844799302</v>
+        <v>380.1137281592219</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25453,28 +25499,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2625665788423932</v>
+        <v>-0.272492555556758</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03710339183373734</v>
+        <v>0.03947627426765676</v>
       </c>
       <c r="M3" t="n">
-        <v>7.849967445506723</v>
+        <v>7.88468294743228</v>
       </c>
       <c r="N3" t="n">
-        <v>91.72307432995753</v>
+        <v>92.8099084999166</v>
       </c>
       <c r="O3" t="n">
-        <v>9.577216418665579</v>
+        <v>9.633789934388055</v>
       </c>
       <c r="P3" t="n">
-        <v>382.6977173959022</v>
+        <v>382.810816178795</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25531,28 +25577,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1984051258958729</v>
+        <v>-0.2084009626319325</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02914813801063287</v>
+        <v>0.03159557484881914</v>
       </c>
       <c r="M4" t="n">
-        <v>7.031927285074575</v>
+        <v>7.070285460538795</v>
       </c>
       <c r="N4" t="n">
-        <v>68.32345039277432</v>
+        <v>69.50583559382393</v>
       </c>
       <c r="O4" t="n">
-        <v>8.265800045535478</v>
+        <v>8.337015988579124</v>
       </c>
       <c r="P4" t="n">
-        <v>382.0906888938449</v>
+        <v>382.2034357732344</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25609,28 +25655,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2971523195651559</v>
+        <v>-0.3051600229264968</v>
       </c>
       <c r="J5" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K5" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06503142350311431</v>
+        <v>0.067785706079866</v>
       </c>
       <c r="M5" t="n">
-        <v>6.803148341822792</v>
+        <v>6.828959736465745</v>
       </c>
       <c r="N5" t="n">
-        <v>66.15365850872945</v>
+        <v>66.86890856912501</v>
       </c>
       <c r="O5" t="n">
-        <v>8.133489934138325</v>
+        <v>8.177341167465437</v>
       </c>
       <c r="P5" t="n">
-        <v>376.6783510981872</v>
+        <v>376.76867305811</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25687,28 +25733,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2910765563594597</v>
+        <v>-0.2964384616083401</v>
       </c>
       <c r="J6" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K6" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09560040585267293</v>
+        <v>0.09835192650061941</v>
       </c>
       <c r="M6" t="n">
-        <v>5.453493360829104</v>
+        <v>5.474761624175706</v>
       </c>
       <c r="N6" t="n">
-        <v>41.76735203252412</v>
+        <v>42.06439169468112</v>
       </c>
       <c r="O6" t="n">
-        <v>6.462766592762276</v>
+        <v>6.485706722839163</v>
       </c>
       <c r="P6" t="n">
-        <v>374.9022116045574</v>
+        <v>374.9626905919955</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25765,28 +25811,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3579976887173762</v>
+        <v>-0.3636682337942305</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1317718394701806</v>
+        <v>0.1347508008937055</v>
       </c>
       <c r="M7" t="n">
-        <v>5.450764108970623</v>
+        <v>5.473448954308333</v>
       </c>
       <c r="N7" t="n">
-        <v>44.00414309791073</v>
+        <v>44.34165605491879</v>
       </c>
       <c r="O7" t="n">
-        <v>6.633561871115</v>
+        <v>6.65895307499</v>
       </c>
       <c r="P7" t="n">
-        <v>383.005282867989</v>
+        <v>383.0692431225164</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25843,28 +25889,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2336127548030375</v>
+        <v>-0.2396618733105562</v>
       </c>
       <c r="J8" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K8" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04219564880169824</v>
+        <v>0.04416331592330769</v>
       </c>
       <c r="M8" t="n">
-        <v>6.592732884239314</v>
+        <v>6.610672453331981</v>
       </c>
       <c r="N8" t="n">
-        <v>64.55414025921758</v>
+        <v>64.90994524919077</v>
       </c>
       <c r="O8" t="n">
-        <v>8.034559120400917</v>
+        <v>8.056670853968825</v>
       </c>
       <c r="P8" t="n">
-        <v>382.4003829478089</v>
+        <v>382.468613277374</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25921,28 +25967,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2136154419333078</v>
+        <v>-0.2194621321995521</v>
       </c>
       <c r="J9" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K9" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03527611213423243</v>
+        <v>0.03705523152279988</v>
       </c>
       <c r="M9" t="n">
-        <v>6.413452178679852</v>
+        <v>6.433827901442467</v>
       </c>
       <c r="N9" t="n">
-        <v>65.02935841884057</v>
+        <v>65.3525230486989</v>
       </c>
       <c r="O9" t="n">
-        <v>8.06407827459782</v>
+        <v>8.084090737287584</v>
       </c>
       <c r="P9" t="n">
-        <v>385.8299246586285</v>
+        <v>385.8958717223593</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25980,7 +26026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J512"/>
+  <dimension ref="A1:J513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52595,6 +52641,58 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-45.76188503439822,170.66602343132777</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-45.76213469612449,170.66683074336726</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-45.762311358690695,170.66766823886923</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-45.76243168073827,170.66853849835147</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-45.76248334926926,170.6694407920886</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-45.76256019654639,170.67033052905487</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-45.76261815044105,170.67120230837486</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-45.762591842878855,170.67208721120667</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18906,6 +18906,258 @@
       <c r="J513" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="C514" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="D514" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="E514" t="n">
+        <v>346.63</v>
+      </c>
+      <c r="F514" t="n">
+        <v>351.32</v>
+      </c>
+      <c r="G514" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="H514" t="n">
+        <v>360.07</v>
+      </c>
+      <c r="I514" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>351.96</v>
+      </c>
+      <c r="C515" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="D515" t="n">
+        <v>351.14</v>
+      </c>
+      <c r="E515" t="n">
+        <v>347.68</v>
+      </c>
+      <c r="F515" t="n">
+        <v>347.84</v>
+      </c>
+      <c r="G515" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="H515" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="I515" t="n">
+        <v>360.82</v>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="C516" t="n">
+        <v>350.57</v>
+      </c>
+      <c r="D516" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="E516" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="F516" t="n">
+        <v>348.63</v>
+      </c>
+      <c r="G516" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="H516" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="I516" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="C517" t="n">
+        <v>349.56</v>
+      </c>
+      <c r="D517" t="n">
+        <v>351.97</v>
+      </c>
+      <c r="E517" t="n">
+        <v>347.46</v>
+      </c>
+      <c r="F517" t="n">
+        <v>347.63</v>
+      </c>
+      <c r="G517" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="H517" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="I517" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>352.65</v>
+      </c>
+      <c r="C518" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="D518" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="E518" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="F518" t="n">
+        <v>349.4</v>
+      </c>
+      <c r="G518" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="H518" t="n">
+        <v>360.64</v>
+      </c>
+      <c r="I518" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>354.41</v>
+      </c>
+      <c r="C519" t="n">
+        <v>354.05</v>
+      </c>
+      <c r="D519" t="n">
+        <v>357.61</v>
+      </c>
+      <c r="E519" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="F519" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="G519" t="n">
+        <v>357.23</v>
+      </c>
+      <c r="H519" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="I519" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="C520" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="D520" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="E520" t="n">
+        <v>352.43</v>
+      </c>
+      <c r="F520" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="G520" t="n">
+        <v>357.71</v>
+      </c>
+      <c r="H520" t="n">
+        <v>363.69</v>
+      </c>
+      <c r="I520" t="n">
+        <v>369.02</v>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18920,7 +19172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25253,6 +25505,76 @@
       </c>
       <c r="B633" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -25421,28 +25743,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2386819539853118</v>
+        <v>-0.2946200618261632</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03580279417014387</v>
+        <v>0.05120697461246215</v>
       </c>
       <c r="M2" t="n">
-        <v>7.335862062742941</v>
+        <v>7.501821957712929</v>
       </c>
       <c r="N2" t="n">
-        <v>79.4596707374865</v>
+        <v>84.44539582535805</v>
       </c>
       <c r="O2" t="n">
-        <v>8.914015410435777</v>
+        <v>9.189417599900336</v>
       </c>
       <c r="P2" t="n">
-        <v>380.1137281592219</v>
+        <v>380.7496414630424</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25499,28 +25821,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.272492555556758</v>
+        <v>-0.3354533456282023</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03947627426765676</v>
+        <v>0.05586862954330374</v>
       </c>
       <c r="M3" t="n">
-        <v>7.88468294743228</v>
+        <v>8.096012788811388</v>
       </c>
       <c r="N3" t="n">
-        <v>92.8099084999166</v>
+        <v>99.04351655063427</v>
       </c>
       <c r="O3" t="n">
-        <v>9.633789934388055</v>
+        <v>9.952060919761005</v>
       </c>
       <c r="P3" t="n">
-        <v>382.810816178795</v>
+        <v>383.5302166544012</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25577,28 +25899,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2084009626319325</v>
+        <v>-0.2678255386324653</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03159557484881914</v>
+        <v>0.04790471907230787</v>
       </c>
       <c r="M4" t="n">
-        <v>7.070285460538795</v>
+        <v>7.285103216311719</v>
       </c>
       <c r="N4" t="n">
-        <v>69.50583559382393</v>
+        <v>75.4595491194974</v>
       </c>
       <c r="O4" t="n">
-        <v>8.337015988579124</v>
+        <v>8.686745600021759</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2034357732344</v>
+        <v>382.8755796316041</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25655,28 +25977,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3051600229264968</v>
+        <v>-0.3555087409194494</v>
       </c>
       <c r="J5" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K5" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.067785706079866</v>
+        <v>0.08622229552937821</v>
       </c>
       <c r="M5" t="n">
-        <v>6.828959736465745</v>
+        <v>6.990810219282453</v>
       </c>
       <c r="N5" t="n">
-        <v>66.86890856912501</v>
+        <v>70.89729405840093</v>
       </c>
       <c r="O5" t="n">
-        <v>8.177341167465437</v>
+        <v>8.420053091186595</v>
       </c>
       <c r="P5" t="n">
-        <v>376.76867305811</v>
+        <v>377.3381724195037</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25733,28 +26055,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2964384616083401</v>
+        <v>-0.3417893715093371</v>
       </c>
       <c r="J6" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K6" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09835192650061941</v>
+        <v>0.1196960124862584</v>
       </c>
       <c r="M6" t="n">
-        <v>5.474761624175706</v>
+        <v>5.667494776316289</v>
       </c>
       <c r="N6" t="n">
-        <v>42.06439169468112</v>
+        <v>45.47557618674127</v>
       </c>
       <c r="O6" t="n">
-        <v>6.485706722839163</v>
+        <v>6.74355812511031</v>
       </c>
       <c r="P6" t="n">
-        <v>374.9626905919955</v>
+        <v>375.4757068597983</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25811,28 +26133,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3636682337942305</v>
+        <v>-0.4104603128313259</v>
       </c>
       <c r="J7" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1347508008937055</v>
+        <v>0.1567088857412482</v>
       </c>
       <c r="M7" t="n">
-        <v>5.473448954308333</v>
+        <v>5.672924451087173</v>
       </c>
       <c r="N7" t="n">
-        <v>44.34165605491879</v>
+        <v>47.98818916922097</v>
       </c>
       <c r="O7" t="n">
-        <v>6.65895307499</v>
+        <v>6.927350804544329</v>
       </c>
       <c r="P7" t="n">
-        <v>383.0692431225164</v>
+        <v>383.5985425388042</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25889,28 +26211,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2396618733105562</v>
+        <v>-0.2798352248149685</v>
       </c>
       <c r="J8" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K8" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04416331592330769</v>
+        <v>0.05810610707198971</v>
       </c>
       <c r="M8" t="n">
-        <v>6.610672453331981</v>
+        <v>6.734392543642682</v>
       </c>
       <c r="N8" t="n">
-        <v>64.90994524919077</v>
+        <v>67.18821148100741</v>
       </c>
       <c r="O8" t="n">
-        <v>8.056670853968825</v>
+        <v>8.196841555197185</v>
       </c>
       <c r="P8" t="n">
-        <v>382.468613277374</v>
+        <v>382.9230220029264</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25967,28 +26289,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2194621321995521</v>
+        <v>-0.2583952486021464</v>
       </c>
       <c r="J9" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K9" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03705523152279988</v>
+        <v>0.04976223199505869</v>
       </c>
       <c r="M9" t="n">
-        <v>6.433827901442467</v>
+        <v>6.573822005862842</v>
       </c>
       <c r="N9" t="n">
-        <v>65.3525230486989</v>
+        <v>67.48536486803663</v>
       </c>
       <c r="O9" t="n">
-        <v>8.084090737287584</v>
+        <v>8.214947648526838</v>
       </c>
       <c r="P9" t="n">
-        <v>385.8958717223593</v>
+        <v>386.3362161686224</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26026,7 +26348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52693,6 +53015,370 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-45.76188997208677,170.6660197234358</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-45.762138335476465,170.66682851780033</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-45.7623170240984,170.66766616674695</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-45.762443018321015,170.6685356111869</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-45.76249983912595,170.6694360213039</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-45.76258302334831,170.67032450856271</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-45.76262137534503,170.6712018778319</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-45.762604336758784,170.67208642603816</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-45.761846488566725,170.66605237678397</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-45.76213403442412,170.66683114801577</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-45.7623081337663,170.6676694183848</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-45.76243371796018,170.66853797956415</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-45.76253052613118,170.66942714304417</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-45.76261460927109,170.670316177873</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-45.76264036644621,170.67119934241097</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-45.7626286054463,170.67208490088944</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-45.761841789797444,170.6660559052562</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-45.76213171847285,170.66683256428547</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-45.76229244494465,170.6676751565666</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-45.762425923371985,170.66853996448924</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-45.76252355982837,170.66942915851212</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-45.76259523303287,170.6703212882973</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-45.76261868792506,170.67120223661772</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-45.7626024491942,170.67208654466077</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-45.76185198373743,170.6660482502648</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-45.76214007243988,170.6668274555978</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-45.762300899476365,170.66767206432462</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-45.76243566660721,170.6685374833328</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-45.76253237793319,170.6694266072868</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-45.7626053192939,170.6703186280769</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-45.76263660405825,170.67119984471148</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-45.7626024491942,170.67208654466077</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-45.76184099339585,170.6660565033023</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-45.76212129669178,170.66683893749757</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-45.762277540563716,170.66768060783613</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-45.762415914412074,170.66854251331256</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-45.76251676988759,170.669431122955</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-45.76258903971463,170.67032292176543</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-45.762616269247054,170.6712025595249</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-45.762583573548255,170.67208773088626</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-45.761826976727356,170.66606702891053</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-45.762102934505116,170.66685016648444</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-45.76225174116665,170.66769004394465</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-45.76239394784486,170.6685481071869</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-45.76250169092802,170.66943548554715</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-45.76257320251499,170.6703270987751</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-45.76259432198369,170.6712054896073</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-45.76255840602018,170.6720893125186</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-45.76180579244219,170.6660829369219</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-45.7620929262857,170.6668562867849</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-45.762249736483724,170.6676907771554</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-45.76239164489828,170.66854869364118</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-45.76250116184172,170.6694356386205</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-45.76256895566811,170.67032821886664</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-45.762588947143655,170.67120620717813</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-45.76255490054305,170.67208953281724</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J520"/>
+  <dimension ref="A1:J524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19156,6 +19156,150 @@
         <v>369.02</v>
       </c>
       <c r="J520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>361.72</v>
+      </c>
+      <c r="C521" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="D521" t="n">
+        <v>359.52</v>
+      </c>
+      <c r="E521" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="F521" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="G521" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="H521" t="n">
+        <v>363.04</v>
+      </c>
+      <c r="I521" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="C522" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="D522" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="E522" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="F522" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="G522" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="H522" t="n">
+        <v>364.05</v>
+      </c>
+      <c r="I522" t="n">
+        <v>369.38</v>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="C523" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="D523" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="E523" t="n">
+        <v>354.79</v>
+      </c>
+      <c r="F523" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="G523" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="H523" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="I523" t="n">
+        <v>369.99</v>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="C524" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="D524" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="E524" t="n">
+        <v>354.79</v>
+      </c>
+      <c r="F524" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="G524" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="H524" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="I524" t="n">
+        <v>369.99</v>
+      </c>
+      <c r="J524" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19172,7 +19316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B640"/>
+  <dimension ref="A1:B645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25575,6 +25719,56 @@
       </c>
       <c r="B640" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -25743,28 +25937,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2946200618261632</v>
+        <v>-0.3058907900457652</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05120697461246215</v>
+        <v>0.05547802478129393</v>
       </c>
       <c r="M2" t="n">
-        <v>7.501821957712929</v>
+        <v>7.500154566636297</v>
       </c>
       <c r="N2" t="n">
-        <v>84.44539582535805</v>
+        <v>84.27908538784291</v>
       </c>
       <c r="O2" t="n">
-        <v>9.189417599900336</v>
+        <v>9.180364120656812</v>
       </c>
       <c r="P2" t="n">
-        <v>380.7496414630424</v>
+        <v>380.8783502427693</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25821,28 +26015,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3354533456282023</v>
+        <v>-0.3602633969197191</v>
       </c>
       <c r="J3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05586862954330374</v>
+        <v>0.06354428609387031</v>
       </c>
       <c r="M3" t="n">
-        <v>8.096012788811388</v>
+        <v>8.159117398313905</v>
       </c>
       <c r="N3" t="n">
-        <v>99.04351655063427</v>
+        <v>100.3815575116134</v>
       </c>
       <c r="O3" t="n">
-        <v>9.952060919761005</v>
+        <v>10.01905971194969</v>
       </c>
       <c r="P3" t="n">
-        <v>383.5302166544012</v>
+        <v>383.8150119970245</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25899,28 +26093,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2678255386324653</v>
+        <v>-0.2903949387828526</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04790471907230787</v>
+        <v>0.0554161717015097</v>
       </c>
       <c r="M4" t="n">
-        <v>7.285103216311719</v>
+        <v>7.349722373532224</v>
       </c>
       <c r="N4" t="n">
-        <v>75.4595491194974</v>
+        <v>76.6582308784655</v>
       </c>
       <c r="O4" t="n">
-        <v>8.686745600021759</v>
+        <v>8.755468627004811</v>
       </c>
       <c r="P4" t="n">
-        <v>382.8755796316041</v>
+        <v>383.1320745708476</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25977,28 +26171,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3555087409194494</v>
+        <v>-0.3754702921167387</v>
       </c>
       <c r="J5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08622229552937821</v>
+        <v>0.09485289933552787</v>
       </c>
       <c r="M5" t="n">
-        <v>6.990810219282453</v>
+        <v>7.042333707363329</v>
       </c>
       <c r="N5" t="n">
-        <v>70.89729405840093</v>
+        <v>71.74579234618672</v>
       </c>
       <c r="O5" t="n">
-        <v>8.420053091186595</v>
+        <v>8.470288799455821</v>
       </c>
       <c r="P5" t="n">
-        <v>377.3381724195037</v>
+        <v>377.5650251369124</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26055,28 +26249,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3417893715093371</v>
+        <v>-0.3629530471747482</v>
       </c>
       <c r="J6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1196960124862584</v>
+        <v>0.1307831341876901</v>
       </c>
       <c r="M6" t="n">
-        <v>5.667494776316289</v>
+        <v>5.750483230626646</v>
       </c>
       <c r="N6" t="n">
-        <v>45.47557618674127</v>
+        <v>46.69324085698125</v>
       </c>
       <c r="O6" t="n">
-        <v>6.74355812511031</v>
+        <v>6.833245265390468</v>
       </c>
       <c r="P6" t="n">
-        <v>375.4757068597983</v>
+        <v>375.7162195795291</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26133,28 +26327,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4104603128313259</v>
+        <v>-0.4310234539612559</v>
       </c>
       <c r="J7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1567088857412482</v>
+        <v>0.1679088853628604</v>
       </c>
       <c r="M7" t="n">
-        <v>5.672924451087173</v>
+        <v>5.750184102510695</v>
       </c>
       <c r="N7" t="n">
-        <v>47.98818916922097</v>
+        <v>49.09934880645952</v>
       </c>
       <c r="O7" t="n">
-        <v>6.927350804544329</v>
+        <v>7.007092749954115</v>
       </c>
       <c r="P7" t="n">
-        <v>383.5985425388042</v>
+        <v>383.8322297280693</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26211,28 +26405,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2798352248149685</v>
+        <v>-0.2956981023602386</v>
       </c>
       <c r="J8" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K8" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05810610707198971</v>
+        <v>0.06456496860660987</v>
       </c>
       <c r="M8" t="n">
-        <v>6.734392543642682</v>
+        <v>6.770010391392261</v>
       </c>
       <c r="N8" t="n">
-        <v>67.18821148100741</v>
+        <v>67.56013076166884</v>
       </c>
       <c r="O8" t="n">
-        <v>8.196841555197185</v>
+        <v>8.219496989577211</v>
       </c>
       <c r="P8" t="n">
-        <v>382.9230220029264</v>
+        <v>383.1032882714499</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26289,28 +26483,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2583952486021464</v>
+        <v>-0.2729740225507806</v>
       </c>
       <c r="J9" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K9" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04976223199505869</v>
+        <v>0.0554350481649436</v>
       </c>
       <c r="M9" t="n">
-        <v>6.573822005862842</v>
+        <v>6.611099561290213</v>
       </c>
       <c r="N9" t="n">
-        <v>67.48536486803663</v>
+        <v>67.71217401601423</v>
       </c>
       <c r="O9" t="n">
-        <v>8.214947648526838</v>
+        <v>8.22874073087822</v>
       </c>
       <c r="P9" t="n">
-        <v>386.3362161686224</v>
+        <v>386.5018952641889</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26348,7 +26542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J520"/>
+  <dimension ref="A1:J524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53379,6 +53573,214 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-45.76176875975717,170.66611074601</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-45.7620829180659,170.6668624070831</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-45.76223509358216,170.6676961327801</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-45.76238482463336,170.66855043044782</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-45.76250724633421,170.66943387827666</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-45.76257276013511,170.6703272154513</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-45.76259476988703,170.67120542980976</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-45.76255966439658,170.67208923343702</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-45.761739850365444,170.66613245501395</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-45.76207166915724,170.66686928609326</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-45.762228295092044,170.6676986193191</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-45.76237809294326,170.6685521446981</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-45.76249604734075,170.66943711832954</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-45.76256426644134,170.67032945563417</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-45.76258572223961,170.67120663772053</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-45.76255166471799,170.6720897361698</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-45.761739850365444,170.66613245501395</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-45.76206596199015,170.66687277617822</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-45.76222106080119,170.66770126525097</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-45.762370741229034,170.66855401683932</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-45.762488287408196,170.66943936340473</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-45.762554268655876,170.67033209251514</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-45.762571389332756,170.67120855124165</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-45.76254618179221,170.67209008073937</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-45.76171540082111,170.66615081495266</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-45.76206596199015,170.66687277617822</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-45.76222890521297,170.6676983961682</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-45.762370741229034,170.66855401683932</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-45.762488287408196,170.66943936340473</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-45.762554268655876,170.67033209251514</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-45.762571389332756,170.67120855124165</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-45.76254618179221,170.67209008073937</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
